--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -2118,13 +2118,13 @@
         <v>35</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>37</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -84,6 +84,9 @@
     <t>向上取整粒度。</t>
   </si>
   <si>
+    <t>目标分 = exp(k0 + kWeek*周数 + kDay*当周过去天数)</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -102,13 +105,13 @@
     <t>int</t>
   </si>
   <si>
-    <t>目标分 = exp(k0 + kBase*基础分 + kWeek*周数 + kDay*当周过去天数)</t>
+    <t>target_score_0</t>
+  </si>
+  <si>
+    <t>TargetScore</t>
   </si>
   <si>
     <t>target_score_1</t>
-  </si>
-  <si>
-    <t>TargetScore</t>
   </si>
   <si>
     <t>target_score_2</t>
@@ -785,11 +788,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1861,344 +1861,584 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.6923076923077" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.3846153846154" style="2" customWidth="1"/>
-    <col min="4" max="4" width="28.9230769230769" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.8461538461538" style="2" customWidth="1"/>
-    <col min="7" max="7" width="34.5384615384615" style="2" customWidth="1"/>
-    <col min="8" max="8" width="27.6923076923077" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.4615384615385" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.9230769230769" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.6153846153846" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.3846153846154" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.6923076923077" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.1538461538462" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.9230769230769" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.8461538461538" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34.5384615384615" style="1" customWidth="1"/>
+    <col min="8" max="8" width="27.6923076923077" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.4615384615385" style="1" customWidth="1"/>
+    <col min="10" max="10" width="25.9230769230769" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.6153846153846" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.3846153846154" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="M2" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:22">
+      <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="F3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>3</v>
+      </c>
+      <c r="R3" s="1">
+        <v>4</v>
+      </c>
+      <c r="S3" s="1">
+        <v>5</v>
+      </c>
+      <c r="T3" s="1">
+        <v>6</v>
+      </c>
+      <c r="U3" s="1">
+        <v>7</v>
+      </c>
+      <c r="V3" s="1">
+        <v>7.5</v>
+      </c>
     </row>
-    <row r="4" spans="2:11">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:22">
+      <c r="B4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>4</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>10</v>
+      </c>
+      <c r="N4" s="1">
+        <f>ROUND(EXP($H4+$D4*$I4+$J4*N$3),-1)</f>
+        <v>50</v>
+      </c>
+      <c r="O4" s="1">
+        <f>ROUND(EXP($H4+$D4*$I4+$J4*O$3),-1)</f>
+        <v>90</v>
+      </c>
+      <c r="P4" s="1">
+        <f>ROUND(EXP($H4+$D4*$I4+$J4*P$3),-1)</f>
+        <v>150</v>
+      </c>
+      <c r="Q4" s="1">
+        <f>ROUND(EXP($H4+$D4*$I4+$J4*Q$3),-1)</f>
+        <v>240</v>
+      </c>
+      <c r="R4" s="1">
+        <f>ROUND(EXP($H4+$D4*$I4+$J4*R$3),-1)</f>
+        <v>400</v>
+      </c>
+      <c r="S4" s="1">
+        <f>ROUND(EXP($H4+$D4*$I4+$J4*S$3),-1)</f>
+        <v>670</v>
+      </c>
+      <c r="T4" s="1">
+        <f>ROUND(EXP($H4+$D4*$I4+$J4*T$3),-1)</f>
+        <v>1100</v>
+      </c>
+      <c r="U4" s="1">
+        <f>ROUND(EXP($H4+$D4*$I4+$J4*U$3),-1)</f>
+        <v>1810</v>
+      </c>
+      <c r="V4" s="1">
+        <f>ROUND(EXP($H4+$D4*$I4+$J4*V$3),-1)</f>
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="B5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F5" s="1">
         <v>0</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G5" s="1">
         <v>0</v>
       </c>
-      <c r="H4" s="2">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="H5" s="1">
+        <v>6</v>
+      </c>
+      <c r="I5" s="1">
         <v>0</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J5" s="1">
         <v>0.33</v>
       </c>
-      <c r="K4" s="2">
-        <v>10</v>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+      <c r="N5" s="1">
+        <f>ROUND(EXP($H5+$D5*$I5+$J5*N$3),-2)</f>
+        <v>400</v>
+      </c>
+      <c r="O5" s="1">
+        <f t="shared" ref="O5:U5" si="0">ROUND(EXP($H5+$D5*$I5+$J5*O$3),-2)</f>
+        <v>600</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" si="0"/>
+        <v>1100</v>
+      </c>
+      <c r="R5" s="1">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="S5" s="1">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="T5" s="1">
+        <f t="shared" si="0"/>
+        <v>2900</v>
+      </c>
+      <c r="U5" s="1">
+        <f t="shared" si="0"/>
+        <v>4100</v>
+      </c>
+      <c r="V5" s="1">
+        <f>ROUND(EXP($H5+$D5*$I5+$J5*V$3),-2)</f>
+        <v>4800</v>
       </c>
     </row>
-    <row r="5" spans="2:11">
-      <c r="B5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    <row r="6" spans="2:22">
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E6" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F6" s="1">
         <v>0</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H5" s="2">
-        <v>8</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="H6" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="I6" s="1">
         <v>0</v>
       </c>
-      <c r="J5" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="K5" s="2">
+      <c r="J6" s="1">
+        <v>0.3626</v>
+      </c>
+      <c r="K6" s="1">
         <v>100</v>
       </c>
+      <c r="N6" s="1">
+        <f>ROUND(EXP($H6+$D6*$I6+$J6*N$3),-2)</f>
+        <v>3300</v>
+      </c>
+      <c r="O6" s="1">
+        <f>ROUND(EXP($H6+$D6*$I6+$J6*O$3),-2)</f>
+        <v>4700</v>
+      </c>
+      <c r="P6" s="1">
+        <f>ROUND(EXP($H6+$D6*$I6+$J6*P$3),-2)</f>
+        <v>6800</v>
+      </c>
+      <c r="Q6" s="1">
+        <f>ROUND(EXP($H6+$D6*$I6+$J6*Q$3),-2)</f>
+        <v>9800</v>
+      </c>
+      <c r="R6" s="1">
+        <f>ROUND(EXP($H6+$D6*$I6+$J6*R$3),-2)</f>
+        <v>14100</v>
+      </c>
+      <c r="S6" s="1">
+        <f>ROUND(EXP($H6+$D6*$I6+$J6*S$3),-2)</f>
+        <v>20200</v>
+      </c>
+      <c r="T6" s="1">
+        <f>ROUND(EXP($H6+$D6*$I6+$J6*T$3),-2)</f>
+        <v>29000</v>
+      </c>
+      <c r="U6" s="1">
+        <f>ROUND(EXP($H6+$D6*$I6+$J6*U$3),-2)</f>
+        <v>41700</v>
+      </c>
+      <c r="V6" s="1">
+        <f>ROUND(EXP($H6+$D6*$I6+$J6*V$3),-2)</f>
+        <v>50000</v>
+      </c>
     </row>
-    <row r="6" spans="2:11">
-      <c r="B6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    <row r="7" spans="2:22">
+      <c r="B7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D7" s="1">
         <v>3</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F7" s="1">
         <v>0</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H7" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="I7" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J7" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="N7" s="1">
+        <f>ROUND(EXP($H7+$D7*$I7+$J7*N$3),-3)</f>
+        <v>36000</v>
+      </c>
+      <c r="O7" s="1">
+        <f t="shared" ref="O7:U7" si="1">ROUND(EXP($H7+$D7*$I7+$J7*O$3),-3)</f>
+        <v>52000</v>
+      </c>
+      <c r="P7" s="1">
+        <f t="shared" si="1"/>
+        <v>75000</v>
+      </c>
+      <c r="Q7" s="1">
+        <f t="shared" si="1"/>
+        <v>107000</v>
+      </c>
+      <c r="R7" s="1">
+        <f t="shared" si="1"/>
+        <v>153000</v>
+      </c>
+      <c r="S7" s="1">
+        <f t="shared" si="1"/>
+        <v>220000</v>
+      </c>
+      <c r="T7" s="1">
+        <f t="shared" si="1"/>
+        <v>315000</v>
+      </c>
+      <c r="U7" s="1">
+        <f t="shared" si="1"/>
+        <v>451000</v>
+      </c>
+      <c r="V7" s="1">
+        <f>ROUND(EXP($H7+$D7*$I7+$J7*V$3),-3)</f>
+        <v>540000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22">
+      <c r="B8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="J6" s="2">
-        <v>0.45</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="2">
-        <v>4</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="F8" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H8" s="1">
+        <v>13</v>
+      </c>
+      <c r="I8" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="J8" s="1">
+        <v>0.324</v>
+      </c>
+      <c r="K8" s="1">
         <v>100000</v>
       </c>
-    </row>
-    <row r="8" spans="2:11">
-      <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="2">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2">
-        <v>10</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1</v>
+      <c r="N8" s="1">
+        <f>ROUND(EXP($H8+$D8*$I8+$J8*N$3),-5)</f>
+        <v>400000</v>
+      </c>
+      <c r="O8" s="1">
+        <f t="shared" ref="O8:V8" si="2">ROUND(EXP($H8+$D8*$I8+$J8*O$3),-5)</f>
+        <v>600000</v>
+      </c>
+      <c r="P8" s="1">
+        <f t="shared" si="2"/>
+        <v>800000</v>
+      </c>
+      <c r="Q8" s="1">
+        <f t="shared" si="2"/>
+        <v>1200000</v>
+      </c>
+      <c r="R8" s="1">
+        <f t="shared" si="2"/>
+        <v>1600000</v>
+      </c>
+      <c r="S8" s="1">
+        <f t="shared" si="2"/>
+        <v>2200000</v>
+      </c>
+      <c r="T8" s="1">
+        <f t="shared" si="2"/>
+        <v>3100000</v>
+      </c>
+      <c r="U8" s="1">
+        <f t="shared" si="2"/>
+        <v>4300000</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" si="2"/>
+        <v>5000000</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>10</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>10</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <v>1</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="1">
         <v>0</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>0</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="1">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="2">
+      <c r="C11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="1">
         <v>10</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F11" s="1">
         <v>10</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G11" s="1">
         <v>1</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H11" s="1">
         <v>0</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I11" s="1">
         <v>0</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J11" s="1">
         <v>0</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K11" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2211,17 +2451,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="20.3846153846154" style="1" customWidth="1"/>
     <col min="3" max="4" width="32.1538461538462" style="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.1538461538462" style="1" customWidth="1"/>
-    <col min="7" max="8" width="29.6923076923077" style="1" customWidth="1"/>
-    <col min="9" max="9" width="53.3846153846154" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="6" max="7" width="15.1538461538462" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.84615384615385" style="1" customWidth="1"/>
+    <col min="9" max="17" width="6.73076923076923" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2232,16 +2472,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2249,56 +2489,245 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>2</v>
+      </c>
+      <c r="L3" s="1">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1">
+        <v>4</v>
+      </c>
+      <c r="N3" s="1">
+        <v>5</v>
+      </c>
+      <c r="O3" s="1">
+        <v>6</v>
+      </c>
+      <c r="P3" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>7.5</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
+    <row r="4" spans="2:17">
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1">
         <v>20</v>
       </c>
       <c r="D4" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1">
         <v>0.2</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <f>$C$4+$D$4*$H4+I$3*$E$4</f>
+        <v>30</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" ref="J4:Q4" si="0">$C$4+$D$4*$H4+J$3*$E$4</f>
+        <v>33</v>
+      </c>
+      <c r="K4" s="1">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="L4" s="1">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="M4" s="1">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="N4" s="1">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="O4" s="1">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="P4" s="1">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="Q4" s="1">
+        <f t="shared" si="0"/>
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="5" spans="8:17">
+      <c r="H5" s="1">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1">
+        <f>$C$4+$D$4*$H5+I$3*$E$4</f>
+        <v>40</v>
+      </c>
+      <c r="J5" s="1">
+        <f>$C$4+$D$4*$H5+J$3*$E$4</f>
+        <v>43</v>
+      </c>
+      <c r="K5" s="1">
+        <f>$C$4+$D$4*$H5+K$3*$E$4</f>
+        <v>46</v>
+      </c>
+      <c r="L5" s="1">
+        <f>$C$4+$D$4*$H5+L$3*$E$4</f>
+        <v>49</v>
+      </c>
+      <c r="M5" s="1">
+        <f>$C$4+$D$4*$H5+M$3*$E$4</f>
+        <v>52</v>
+      </c>
+      <c r="N5" s="1">
+        <f>$C$4+$D$4*$H5+N$3*$E$4</f>
+        <v>55</v>
+      </c>
+      <c r="O5" s="1">
+        <f>$C$4+$D$4*$H5+O$3*$E$4</f>
+        <v>58</v>
+      </c>
+      <c r="P5" s="1">
+        <f>$C$4+$D$4*$H5+P$3*$E$4</f>
+        <v>61</v>
+      </c>
+      <c r="Q5" s="1">
+        <f>$C$4+$D$4*$H5+Q$3*$E$4</f>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="6" spans="8:17">
+      <c r="H6" s="1">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1">
+        <f>$C$4+$D$4*$H6+I$3*$E$4</f>
+        <v>50</v>
+      </c>
+      <c r="J6" s="1">
+        <f>$C$4+$D$4*$H6+J$3*$E$4</f>
+        <v>53</v>
+      </c>
+      <c r="K6" s="1">
+        <f>$C$4+$D$4*$H6+K$3*$E$4</f>
+        <v>56</v>
+      </c>
+      <c r="L6" s="1">
+        <f>$C$4+$D$4*$H6+L$3*$E$4</f>
+        <v>59</v>
+      </c>
+      <c r="M6" s="1">
+        <f>$C$4+$D$4*$H6+M$3*$E$4</f>
+        <v>62</v>
+      </c>
+      <c r="N6" s="1">
+        <f>$C$4+$D$4*$H6+N$3*$E$4</f>
+        <v>65</v>
+      </c>
+      <c r="O6" s="1">
+        <f>$C$4+$D$4*$H6+O$3*$E$4</f>
+        <v>68</v>
+      </c>
+      <c r="P6" s="1">
+        <f>$C$4+$D$4*$H6+P$3*$E$4</f>
+        <v>71</v>
+      </c>
+      <c r="Q6" s="1">
+        <f>$C$4+$D$4*$H6+Q$3*$E$4</f>
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="7" spans="8:17">
+      <c r="H7" s="1">
+        <v>4</v>
+      </c>
+      <c r="I7" s="1">
+        <f>$C$4+$D$4*$H7+I$3*$E$4</f>
+        <v>60</v>
+      </c>
+      <c r="J7" s="1">
+        <f>$C$4+$D$4*$H7+J$3*$E$4</f>
+        <v>63</v>
+      </c>
+      <c r="K7" s="1">
+        <f>$C$4+$D$4*$H7+K$3*$E$4</f>
+        <v>66</v>
+      </c>
+      <c r="L7" s="1">
+        <f>$C$4+$D$4*$H7+L$3*$E$4</f>
+        <v>69</v>
+      </c>
+      <c r="M7" s="1">
+        <f>$C$4+$D$4*$H7+M$3*$E$4</f>
+        <v>72</v>
+      </c>
+      <c r="N7" s="1">
+        <f>$C$4+$D$4*$H7+N$3*$E$4</f>
+        <v>75</v>
+      </c>
+      <c r="O7" s="1">
+        <f>$C$4+$D$4*$H7+O$3*$E$4</f>
+        <v>78</v>
+      </c>
+      <c r="P7" s="1">
+        <f>$C$4+$D$4*$H7+P$3*$E$4</f>
+        <v>81</v>
+      </c>
+      <c r="Q7" s="1">
+        <f>$C$4+$D$4*$H7+Q$3*$E$4</f>
+        <v>82.5</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240"/>
+    <workbookView windowHeight="15280"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
@@ -2047,40 +2047,40 @@
         <v>10</v>
       </c>
       <c r="N4" s="1">
-        <f>ROUND(EXP($H4+$D4*$I4+$J4*N$3),-1)</f>
-        <v>50</v>
+        <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*N$3),-1)</f>
+        <v>60</v>
       </c>
       <c r="O4" s="1">
-        <f>ROUND(EXP($H4+$D4*$I4+$J4*O$3),-1)</f>
-        <v>90</v>
+        <f t="shared" ref="O4:V4" si="0">ROUNDUP(EXP($H4+$D4*$I4+$J4*O$3),-1)</f>
+        <v>100</v>
       </c>
       <c r="P4" s="1">
-        <f>ROUND(EXP($H4+$D4*$I4+$J4*P$3),-1)</f>
+        <f t="shared" si="0"/>
         <v>150</v>
       </c>
       <c r="Q4" s="1">
-        <f>ROUND(EXP($H4+$D4*$I4+$J4*Q$3),-1)</f>
-        <v>240</v>
+        <f t="shared" si="0"/>
+        <v>250</v>
       </c>
       <c r="R4" s="1">
-        <f>ROUND(EXP($H4+$D4*$I4+$J4*R$3),-1)</f>
-        <v>400</v>
+        <f t="shared" si="0"/>
+        <v>410</v>
       </c>
       <c r="S4" s="1">
-        <f>ROUND(EXP($H4+$D4*$I4+$J4*S$3),-1)</f>
+        <f t="shared" si="0"/>
         <v>670</v>
       </c>
       <c r="T4" s="1">
-        <f>ROUND(EXP($H4+$D4*$I4+$J4*T$3),-1)</f>
+        <f t="shared" si="0"/>
         <v>1100</v>
       </c>
       <c r="U4" s="1">
-        <f>ROUND(EXP($H4+$D4*$I4+$J4*U$3),-1)</f>
+        <f t="shared" si="0"/>
         <v>1810</v>
       </c>
       <c r="V4" s="1">
-        <f>ROUND(EXP($H4+$D4*$I4+$J4*V$3),-1)</f>
-        <v>2320</v>
+        <f t="shared" si="0"/>
+        <v>2330</v>
       </c>
     </row>
     <row r="5" spans="2:22">
@@ -2103,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
@@ -2115,40 +2115,40 @@
         <v>100</v>
       </c>
       <c r="N5" s="1">
-        <f>ROUND(EXP($H5+$D5*$I5+$J5*N$3),-2)</f>
+        <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*N$3),-2)</f>
+        <v>300</v>
+      </c>
+      <c r="O5" s="1">
+        <f t="shared" ref="O5:V5" si="1">ROUNDUP(EXP($H5+$D5*$I5+$J5*O$3),-2)</f>
         <v>400</v>
       </c>
-      <c r="O5" s="1">
-        <f t="shared" ref="O5:U5" si="0">ROUND(EXP($H5+$D5*$I5+$J5*O$3),-2)</f>
-        <v>600</v>
-      </c>
       <c r="P5" s="1">
-        <f t="shared" si="0"/>
-        <v>800</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="Q5" s="1">
-        <f t="shared" si="0"/>
-        <v>1100</v>
+        <f t="shared" si="1"/>
+        <v>700</v>
       </c>
       <c r="R5" s="1">
-        <f t="shared" si="0"/>
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>1000</v>
       </c>
       <c r="S5" s="1">
-        <f t="shared" si="0"/>
-        <v>2100</v>
+        <f t="shared" si="1"/>
+        <v>1300</v>
       </c>
       <c r="T5" s="1">
-        <f t="shared" si="0"/>
-        <v>2900</v>
+        <f t="shared" si="1"/>
+        <v>1800</v>
       </c>
       <c r="U5" s="1">
-        <f t="shared" si="0"/>
-        <v>4100</v>
+        <f t="shared" si="1"/>
+        <v>2500</v>
       </c>
       <c r="V5" s="1">
-        <f>ROUND(EXP($H5+$D5*$I5+$J5*V$3),-2)</f>
-        <v>4800</v>
+        <f t="shared" si="1"/>
+        <v>3000</v>
       </c>
     </row>
     <row r="6" spans="2:22">
@@ -2171,52 +2171,52 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>0.3626</v>
+        <v>0.375</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="N6" s="1">
-        <f>ROUND(EXP($H6+$D6*$I6+$J6*N$3),-2)</f>
-        <v>3300</v>
+        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*N$3),-3)</f>
+        <v>2000</v>
       </c>
       <c r="O6" s="1">
-        <f>ROUND(EXP($H6+$D6*$I6+$J6*O$3),-2)</f>
-        <v>4700</v>
+        <f t="shared" ref="O6:V6" si="2">ROUNDUP(EXP($H6+$D6*$I6+$J6*O$3),-3)</f>
+        <v>3000</v>
       </c>
       <c r="P6" s="1">
-        <f>ROUND(EXP($H6+$D6*$I6+$J6*P$3),-2)</f>
-        <v>6800</v>
+        <f t="shared" si="2"/>
+        <v>4000</v>
       </c>
       <c r="Q6" s="1">
-        <f>ROUND(EXP($H6+$D6*$I6+$J6*Q$3),-2)</f>
-        <v>9800</v>
+        <f t="shared" si="2"/>
+        <v>6000</v>
       </c>
       <c r="R6" s="1">
-        <f>ROUND(EXP($H6+$D6*$I6+$J6*R$3),-2)</f>
-        <v>14100</v>
+        <f t="shared" si="2"/>
+        <v>9000</v>
       </c>
       <c r="S6" s="1">
-        <f>ROUND(EXP($H6+$D6*$I6+$J6*S$3),-2)</f>
-        <v>20200</v>
+        <f t="shared" si="2"/>
+        <v>12000</v>
       </c>
       <c r="T6" s="1">
-        <f>ROUND(EXP($H6+$D6*$I6+$J6*T$3),-2)</f>
-        <v>29000</v>
+        <f t="shared" si="2"/>
+        <v>18000</v>
       </c>
       <c r="U6" s="1">
-        <f>ROUND(EXP($H6+$D6*$I6+$J6*U$3),-2)</f>
-        <v>41700</v>
+        <f t="shared" si="2"/>
+        <v>25000</v>
       </c>
       <c r="V6" s="1">
-        <f>ROUND(EXP($H6+$D6*$I6+$J6*V$3),-2)</f>
-        <v>50000</v>
+        <f t="shared" si="2"/>
+        <v>31000</v>
       </c>
     </row>
     <row r="7" spans="2:22">
@@ -2239,52 +2239,52 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>0.36</v>
+        <v>0.373</v>
       </c>
       <c r="K7" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="N7" s="1">
-        <f>ROUND(EXP($H7+$D7*$I7+$J7*N$3),-3)</f>
-        <v>36000</v>
+        <f>ROUNDUP(EXP($H7+$D7*$I7+$J7*N$3),-4)</f>
+        <v>30000</v>
       </c>
       <c r="O7" s="1">
-        <f t="shared" ref="O7:U7" si="1">ROUND(EXP($H7+$D7*$I7+$J7*O$3),-3)</f>
-        <v>52000</v>
+        <f t="shared" ref="O7:V7" si="3">ROUNDUP(EXP($H7+$D7*$I7+$J7*O$3),-4)</f>
+        <v>40000</v>
       </c>
       <c r="P7" s="1">
-        <f t="shared" si="1"/>
-        <v>75000</v>
+        <f t="shared" si="3"/>
+        <v>50000</v>
       </c>
       <c r="Q7" s="1">
-        <f t="shared" si="1"/>
-        <v>107000</v>
+        <f t="shared" si="3"/>
+        <v>70000</v>
       </c>
       <c r="R7" s="1">
-        <f t="shared" si="1"/>
-        <v>153000</v>
+        <f t="shared" si="3"/>
+        <v>100000</v>
       </c>
       <c r="S7" s="1">
-        <f t="shared" si="1"/>
-        <v>220000</v>
+        <f t="shared" si="3"/>
+        <v>150000</v>
       </c>
       <c r="T7" s="1">
-        <f t="shared" si="1"/>
-        <v>315000</v>
+        <f t="shared" si="3"/>
+        <v>210000</v>
       </c>
       <c r="U7" s="1">
-        <f t="shared" si="1"/>
-        <v>451000</v>
+        <f t="shared" si="3"/>
+        <v>300000</v>
       </c>
       <c r="V7" s="1">
-        <f>ROUND(EXP($H7+$D7*$I7+$J7*V$3),-3)</f>
-        <v>540000</v>
+        <f t="shared" si="3"/>
+        <v>370000</v>
       </c>
     </row>
     <row r="8" spans="2:22">
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -2320,39 +2320,39 @@
       </c>
       <c r="N8" s="1">
         <f>ROUND(EXP($H8+$D8*$I8+$J8*N$3),-5)</f>
+        <v>200000</v>
+      </c>
+      <c r="O8" s="1">
+        <f t="shared" ref="O8:V8" si="4">ROUND(EXP($H8+$D8*$I8+$J8*O$3),-5)</f>
+        <v>200000</v>
+      </c>
+      <c r="P8" s="1">
+        <f t="shared" si="4"/>
+        <v>300000</v>
+      </c>
+      <c r="Q8" s="1">
+        <f t="shared" si="4"/>
         <v>400000</v>
       </c>
-      <c r="O8" s="1">
-        <f t="shared" ref="O8:V8" si="2">ROUND(EXP($H8+$D8*$I8+$J8*O$3),-5)</f>
+      <c r="R8" s="1">
+        <f t="shared" si="4"/>
         <v>600000</v>
       </c>
-      <c r="P8" s="1">
-        <f t="shared" si="2"/>
+      <c r="S8" s="1">
+        <f t="shared" si="4"/>
         <v>800000</v>
       </c>
-      <c r="Q8" s="1">
-        <f t="shared" si="2"/>
-        <v>1200000</v>
-      </c>
-      <c r="R8" s="1">
-        <f t="shared" si="2"/>
+      <c r="T8" s="1">
+        <f t="shared" si="4"/>
+        <v>1100000</v>
+      </c>
+      <c r="U8" s="1">
+        <f t="shared" si="4"/>
         <v>1600000</v>
       </c>
-      <c r="S8" s="1">
-        <f t="shared" si="2"/>
-        <v>2200000</v>
-      </c>
-      <c r="T8" s="1">
-        <f t="shared" si="2"/>
-        <v>3100000</v>
-      </c>
-      <c r="U8" s="1">
-        <f t="shared" si="2"/>
-        <v>4300000</v>
-      </c>
       <c r="V8" s="1">
-        <f t="shared" si="2"/>
-        <v>5000000</v>
+        <f t="shared" si="4"/>
+        <v>1800000</v>
       </c>
     </row>
     <row r="9" spans="2:11">

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15340"/>
+    <workbookView windowHeight="15360"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
@@ -1993,7 +1993,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -2215,7 +2215,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="5" spans="2:22">
+    <row r="5" spans="2:27">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -2256,34 +2256,43 @@
       </c>
       <c r="P5" s="1">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Q5" s="1">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="S5" s="1">
         <f t="shared" si="1"/>
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" si="1"/>
-        <v>2700</v>
+        <v>2000</v>
       </c>
       <c r="U5" s="1">
         <f t="shared" si="1"/>
-        <v>4100</v>
+        <v>2900</v>
       </c>
       <c r="V5" s="1">
         <f t="shared" si="1"/>
-        <v>5000</v>
+        <v>3400</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>0.4</v>
       </c>
     </row>
-    <row r="6" spans="2:22">
+    <row r="6" spans="2:27">
       <c r="B6" s="1" t="s">
         <v>32</v>
       </c>
@@ -2303,55 +2312,64 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="K6" s="1">
         <v>1000</v>
       </c>
       <c r="N6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*N$3),-3)</f>
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="O6" s="1">
         <f t="shared" ref="O6:V6" si="2">ROUNDUP(EXP($H6+$D6*$I6+$J6*O$3),-3)</f>
+        <v>3000</v>
+      </c>
+      <c r="P6" s="1">
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
-      <c r="P6" s="1">
+      <c r="Q6" s="1">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="Q6" s="1">
-        <f t="shared" si="2"/>
-        <v>9000</v>
-      </c>
       <c r="R6" s="1">
         <f t="shared" si="2"/>
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="S6" s="1">
         <f t="shared" si="2"/>
+        <v>11000</v>
+      </c>
+      <c r="T6" s="1">
+        <f t="shared" si="2"/>
+        <v>15000</v>
+      </c>
+      <c r="U6" s="1">
+        <f t="shared" si="2"/>
         <v>21000</v>
       </c>
-      <c r="T6" s="1">
-        <f t="shared" si="2"/>
-        <v>33000</v>
-      </c>
-      <c r="U6" s="1">
-        <f t="shared" si="2"/>
-        <v>52000</v>
-      </c>
       <c r="V6" s="1">
         <f t="shared" si="2"/>
-        <v>65000</v>
+        <v>25000</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0.45</v>
       </c>
     </row>
-    <row r="7" spans="2:22">
+    <row r="7" spans="2:27">
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
@@ -2371,55 +2389,64 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>0.452</v>
+        <v>0.4</v>
       </c>
       <c r="K7" s="1">
         <v>10000</v>
       </c>
       <c r="N7" s="1">
         <f>ROUNDUP(EXP($H7+$D7*$I7+$J7*N$3),-4)</f>
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="O7" s="1">
         <f t="shared" ref="O7:V7" si="3">ROUNDUP(EXP($H7+$D7*$I7+$J7*O$3),-4)</f>
+        <v>20000</v>
+      </c>
+      <c r="P7" s="1">
+        <f t="shared" si="3"/>
+        <v>30000</v>
+      </c>
+      <c r="Q7" s="1">
+        <f t="shared" si="3"/>
+        <v>50000</v>
+      </c>
+      <c r="R7" s="1">
+        <f t="shared" si="3"/>
         <v>70000</v>
       </c>
-      <c r="P7" s="1">
+      <c r="S7" s="1">
         <f t="shared" si="3"/>
         <v>100000</v>
       </c>
-      <c r="Q7" s="1">
-        <f t="shared" si="3"/>
-        <v>160000</v>
-      </c>
-      <c r="R7" s="1">
-        <f t="shared" si="3"/>
-        <v>250000</v>
-      </c>
-      <c r="S7" s="1">
-        <f t="shared" si="3"/>
-        <v>390000</v>
-      </c>
       <c r="T7" s="1">
         <f t="shared" si="3"/>
-        <v>610000</v>
+        <v>150000</v>
       </c>
       <c r="U7" s="1">
         <f t="shared" si="3"/>
-        <v>950000</v>
+        <v>220000</v>
       </c>
       <c r="V7" s="1">
         <f t="shared" si="3"/>
-        <v>1200000</v>
+        <v>270000</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0.452</v>
       </c>
     </row>
-    <row r="8" spans="2:22">
+    <row r="8" spans="2:27">
       <c r="B8" s="1" t="s">
         <v>34</v>
       </c>
@@ -2439,52 +2466,61 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>13.6</v>
+        <v>12</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>0.428</v>
+        <v>0.35</v>
       </c>
       <c r="K8" s="1">
         <v>100000</v>
       </c>
       <c r="N8" s="1">
         <f>ROUND(EXP($H8+$D8*$I8+$J8*N$3),-5)</f>
-        <v>800000</v>
+        <v>200000</v>
       </c>
       <c r="O8" s="1">
         <f t="shared" ref="O8:V8" si="4">ROUND(EXP($H8+$D8*$I8+$J8*O$3),-5)</f>
-        <v>1200000</v>
+        <v>200000</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>300000</v>
       </c>
       <c r="Q8" s="1">
         <f t="shared" si="4"/>
-        <v>2900000</v>
+        <v>500000</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="4"/>
-        <v>4500000</v>
+        <v>700000</v>
       </c>
       <c r="S8" s="1">
         <f t="shared" si="4"/>
-        <v>6900000</v>
+        <v>900000</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" si="4"/>
-        <v>10500000</v>
+        <v>1300000</v>
       </c>
       <c r="U8" s="1">
         <f t="shared" si="4"/>
-        <v>16100000</v>
+        <v>1900000</v>
       </c>
       <c r="V8" s="1">
         <f t="shared" si="4"/>
-        <v>20000000</v>
+        <v>2200000</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>13.6</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0.428</v>
       </c>
     </row>
     <row r="9" spans="2:11">

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15360"/>
+    <workbookView windowHeight="15400"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
@@ -2235,52 +2235,52 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
       </c>
       <c r="N5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*N$3),-2)</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O5" s="1">
         <f t="shared" ref="O5:V5" si="1">ROUNDUP(EXP($H5+$D5*$I5+$J5*O$3),-2)</f>
+        <v>300</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="P5" s="1">
+      <c r="R5" s="1">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="S5" s="1">
         <f t="shared" si="1"/>
         <v>700</v>
       </c>
-      <c r="R5" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="S5" s="1">
+      <c r="T5" s="1">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+      <c r="U5" s="1">
+        <f t="shared" si="1"/>
+        <v>1300</v>
+      </c>
+      <c r="V5" s="1">
         <f t="shared" si="1"/>
         <v>1500</v>
-      </c>
-      <c r="T5" s="1">
-        <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-      <c r="U5" s="1">
-        <f t="shared" si="1"/>
-        <v>2900</v>
-      </c>
-      <c r="V5" s="1">
-        <f t="shared" si="1"/>
-        <v>3400</v>
       </c>
       <c r="Y5" s="1">
         <v>5.5</v>
@@ -2312,52 +2312,52 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K6" s="1">
+        <v>100</v>
+      </c>
+      <c r="N6" s="1">
+        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*N$3),-2)</f>
         <v>1000</v>
       </c>
-      <c r="N6" s="1">
-        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*N$3),-3)</f>
-        <v>2000</v>
-      </c>
       <c r="O6" s="1">
-        <f t="shared" ref="O6:V6" si="2">ROUNDUP(EXP($H6+$D6*$I6+$J6*O$3),-3)</f>
-        <v>3000</v>
+        <f t="shared" ref="O6:V6" si="2">ROUNDUP(EXP($H6+$D6*$I6+$J6*O$3),-2)</f>
+        <v>1400</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="2"/>
-        <v>4000</v>
+        <v>1900</v>
       </c>
       <c r="Q6" s="1">
         <f t="shared" si="2"/>
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="2"/>
-        <v>8000</v>
+        <v>3300</v>
       </c>
       <c r="S6" s="1">
         <f t="shared" si="2"/>
-        <v>11000</v>
+        <v>4500</v>
       </c>
       <c r="T6" s="1">
         <f t="shared" si="2"/>
-        <v>15000</v>
+        <v>6100</v>
       </c>
       <c r="U6" s="1">
         <f t="shared" si="2"/>
-        <v>21000</v>
+        <v>8200</v>
       </c>
       <c r="V6" s="1">
         <f t="shared" si="2"/>
-        <v>25000</v>
+        <v>9500</v>
       </c>
       <c r="Y6" s="1">
         <v>7.7</v>
@@ -2389,52 +2389,52 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K7" s="1">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="N7" s="1">
-        <f>ROUNDUP(EXP($H7+$D7*$I7+$J7*N$3),-4)</f>
-        <v>20000</v>
+        <f>ROUNDUP(EXP($H7+$D7*$I7+$J7*N$3),-3)</f>
+        <v>6000</v>
       </c>
       <c r="O7" s="1">
         <f t="shared" ref="O7:V7" si="3">ROUNDUP(EXP($H7+$D7*$I7+$J7*O$3),-4)</f>
+        <v>10000</v>
+      </c>
+      <c r="P7" s="1">
+        <f t="shared" si="3"/>
+        <v>10000</v>
+      </c>
+      <c r="Q7" s="1">
+        <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="P7" s="1">
+      <c r="R7" s="1">
+        <f t="shared" si="3"/>
+        <v>20000</v>
+      </c>
+      <c r="S7" s="1">
         <f t="shared" si="3"/>
         <v>30000</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="T7" s="1">
+        <f t="shared" si="3"/>
+        <v>40000</v>
+      </c>
+      <c r="U7" s="1">
         <f t="shared" si="3"/>
         <v>50000</v>
       </c>
-      <c r="R7" s="1">
-        <f t="shared" si="3"/>
-        <v>70000</v>
-      </c>
-      <c r="S7" s="1">
-        <f t="shared" si="3"/>
-        <v>100000</v>
-      </c>
-      <c r="T7" s="1">
-        <f t="shared" si="3"/>
-        <v>150000</v>
-      </c>
-      <c r="U7" s="1">
-        <f t="shared" si="3"/>
-        <v>220000</v>
-      </c>
       <c r="V7" s="1">
         <f t="shared" si="3"/>
-        <v>270000</v>
+        <v>60000</v>
       </c>
       <c r="Y7" s="1">
         <v>10.6</v>
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -2475,43 +2475,43 @@
         <v>0.35</v>
       </c>
       <c r="K8" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="N8" s="1">
-        <f>ROUND(EXP($H8+$D8*$I8+$J8*N$3),-5)</f>
-        <v>200000</v>
+        <f>ROUND(EXP($H8+$D8*$I8+$J8*N$3),-4)</f>
+        <v>40000</v>
       </c>
       <c r="O8" s="1">
-        <f t="shared" ref="O8:V8" si="4">ROUND(EXP($H8+$D8*$I8+$J8*O$3),-5)</f>
-        <v>200000</v>
+        <f t="shared" ref="O8:V8" si="4">ROUND(EXP($H8+$D8*$I8+$J8*O$3),-4)</f>
+        <v>50000</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="4"/>
-        <v>300000</v>
+        <v>70000</v>
       </c>
       <c r="Q8" s="1">
         <f t="shared" si="4"/>
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="4"/>
-        <v>700000</v>
+        <v>150000</v>
       </c>
       <c r="S8" s="1">
         <f t="shared" si="4"/>
-        <v>900000</v>
+        <v>210000</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" si="4"/>
-        <v>1300000</v>
+        <v>300000</v>
       </c>
       <c r="U8" s="1">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>420000</v>
       </c>
       <c r="V8" s="1">
         <f t="shared" si="4"/>
-        <v>2200000</v>
+        <v>500000</v>
       </c>
       <c r="Y8" s="1">
         <v>13.6</v>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15400"/>
+    <workbookView windowHeight="15240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -105,22 +105,16 @@
     <t>int</t>
   </si>
   <si>
-    <t>target_score_0</t>
+    <t>target_score_1</t>
   </si>
   <si>
     <t>TargetScore</t>
   </si>
   <si>
-    <t>target_score_1</t>
-  </si>
-  <si>
     <t>target_score_2</t>
   </si>
   <si>
     <t>target_score_3</t>
-  </si>
-  <si>
-    <t>target_score_4</t>
   </si>
   <si>
     <t>hidden_dish</t>
@@ -1993,7 +1987,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -2147,7 +2141,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="4" spans="2:22">
+    <row r="4" spans="2:27">
       <c r="B4" s="1" t="s">
         <v>29</v>
       </c>
@@ -2155,7 +2149,7 @@
         <v>30</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -2167,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
@@ -2176,43 +2170,52 @@
         <v>0.5</v>
       </c>
       <c r="K4" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="N4" s="1">
-        <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*N$3),-1)</f>
-        <v>60</v>
+        <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*N$3),-2)</f>
+        <v>300</v>
       </c>
       <c r="O4" s="1">
-        <f t="shared" ref="O4:V4" si="0">ROUNDUP(EXP($H4+$D4*$I4+$J4*O$3),-1)</f>
-        <v>100</v>
+        <f t="shared" ref="O4:V4" si="0">ROUNDUP(EXP($H4+$D4*$I4+$J4*O$3),-2)</f>
+        <v>400</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="Q4" s="1">
         <f t="shared" si="0"/>
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="0"/>
-        <v>410</v>
+        <v>1500</v>
       </c>
       <c r="S4" s="1">
         <f t="shared" si="0"/>
-        <v>670</v>
+        <v>2500</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" si="0"/>
-        <v>1100</v>
+        <v>4100</v>
       </c>
       <c r="U4" s="1">
         <f t="shared" si="0"/>
-        <v>1810</v>
+        <v>6700</v>
       </c>
       <c r="V4" s="1">
         <f t="shared" si="0"/>
-        <v>2330</v>
+        <v>8600</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="2:27">
@@ -2223,7 +2226,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -2235,61 +2238,61 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>5</v>
+        <v>8.9</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>0.3</v>
+        <v>0.4945</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="N5" s="1">
-        <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*N$3),-2)</f>
-        <v>200</v>
+        <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*N$3),-3)</f>
+        <v>8000</v>
       </c>
       <c r="O5" s="1">
-        <f t="shared" ref="O5:V5" si="1">ROUNDUP(EXP($H5+$D5*$I5+$J5*O$3),-2)</f>
-        <v>300</v>
+        <f t="shared" ref="O5:V5" si="1">ROUNDUP(EXP($H5+$D5*$I5+$J5*O$3),-3)</f>
+        <v>13000</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>20000</v>
       </c>
       <c r="Q5" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>33000</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>53000</v>
       </c>
       <c r="S5" s="1">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>87000</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>143000</v>
       </c>
       <c r="U5" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>234000</v>
       </c>
       <c r="V5" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>300000</v>
       </c>
       <c r="Y5" s="1">
-        <v>5.5</v>
+        <v>7.7</v>
       </c>
       <c r="Z5" s="1">
         <v>0</v>
       </c>
       <c r="AA5" s="1">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="6" spans="2:27">
@@ -2300,7 +2303,7 @@
         <v>30</v>
       </c>
       <c r="D6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -2312,223 +2315,127 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>6.9</v>
+        <v>12.4</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>0.3</v>
+        <v>0.4957</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="N6" s="1">
-        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*N$3),-2)</f>
-        <v>1000</v>
+        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*N$3),-4)</f>
+        <v>250000</v>
       </c>
       <c r="O6" s="1">
-        <f t="shared" ref="O6:V6" si="2">ROUNDUP(EXP($H6+$D6*$I6+$J6*O$3),-2)</f>
-        <v>1400</v>
+        <f t="shared" ref="O6:V6" si="2">ROUNDUP(EXP($H6+$D6*$I6+$J6*O$3),-4)</f>
+        <v>400000</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="2"/>
-        <v>1900</v>
+        <v>660000</v>
       </c>
       <c r="Q6" s="1">
         <f t="shared" si="2"/>
-        <v>2500</v>
+        <v>1080000</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="2"/>
-        <v>3300</v>
+        <v>1770000</v>
       </c>
       <c r="S6" s="1">
         <f t="shared" si="2"/>
-        <v>4500</v>
+        <v>2900000</v>
       </c>
       <c r="T6" s="1">
         <f t="shared" si="2"/>
-        <v>6100</v>
+        <v>4760000</v>
       </c>
       <c r="U6" s="1">
         <f t="shared" si="2"/>
-        <v>8200</v>
+        <v>7810000</v>
       </c>
       <c r="V6" s="1">
         <f t="shared" si="2"/>
-        <v>9500</v>
+        <v>10000000</v>
       </c>
       <c r="Y6" s="1">
-        <v>7.7</v>
+        <v>10.6</v>
       </c>
       <c r="Z6" s="1">
         <v>0</v>
       </c>
       <c r="AA6" s="1">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
     </row>
-    <row r="7" spans="2:27">
+    <row r="7" spans="2:11">
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="1">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1">
+        <v>10</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
         <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>8.6</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>1000</v>
-      </c>
-      <c r="N7" s="1">
-        <f>ROUNDUP(EXP($H7+$D7*$I7+$J7*N$3),-3)</f>
-        <v>6000</v>
-      </c>
-      <c r="O7" s="1">
-        <f t="shared" ref="O7:V7" si="3">ROUNDUP(EXP($H7+$D7*$I7+$J7*O$3),-4)</f>
-        <v>10000</v>
-      </c>
-      <c r="P7" s="1">
-        <f t="shared" si="3"/>
-        <v>10000</v>
-      </c>
-      <c r="Q7" s="1">
-        <f t="shared" si="3"/>
-        <v>20000</v>
-      </c>
-      <c r="R7" s="1">
-        <f t="shared" si="3"/>
-        <v>20000</v>
-      </c>
-      <c r="S7" s="1">
-        <f t="shared" si="3"/>
-        <v>30000</v>
-      </c>
-      <c r="T7" s="1">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-      <c r="U7" s="1">
-        <f t="shared" si="3"/>
-        <v>50000</v>
-      </c>
-      <c r="V7" s="1">
-        <f t="shared" si="3"/>
-        <v>60000</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>10.6</v>
-      </c>
-      <c r="Z7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1">
+        <v>10</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
         <v>0</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>0.452</v>
-      </c>
-    </row>
-    <row r="8" spans="2:27">
-      <c r="B8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>10.5</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>10000</v>
-      </c>
-      <c r="N8" s="1">
-        <f>ROUND(EXP($H8+$D8*$I8+$J8*N$3),-4)</f>
-        <v>40000</v>
-      </c>
-      <c r="O8" s="1">
-        <f t="shared" ref="O8:V8" si="4">ROUND(EXP($H8+$D8*$I8+$J8*O$3),-4)</f>
-        <v>50000</v>
-      </c>
-      <c r="P8" s="1">
-        <f t="shared" si="4"/>
-        <v>70000</v>
-      </c>
-      <c r="Q8" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
-      </c>
-      <c r="R8" s="1">
-        <f t="shared" si="4"/>
-        <v>150000</v>
-      </c>
-      <c r="S8" s="1">
-        <f t="shared" si="4"/>
-        <v>210000</v>
-      </c>
-      <c r="T8" s="1">
-        <f t="shared" si="4"/>
-        <v>300000</v>
-      </c>
-      <c r="U8" s="1">
-        <f t="shared" si="4"/>
-        <v>420000</v>
-      </c>
-      <c r="V8" s="1">
-        <f t="shared" si="4"/>
-        <v>500000</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>13.6</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>0.428</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:11">
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9" s="1">
         <v>10</v>
@@ -2549,64 +2456,6 @@
         <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="1">
-        <v>10</v>
-      </c>
-      <c r="F10" s="1">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="1">
-        <v>10</v>
-      </c>
-      <c r="F11" s="1">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2619,8 +2468,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="20.3846153846154" style="1" customWidth="1"/>
@@ -2640,16 +2489,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2657,19 +2506,19 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -2721,7 +2570,7 @@
     </row>
     <row r="4" spans="2:17">
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1">
         <v>20</v>
@@ -2855,47 +2704,6 @@
       <c r="Q6" s="1">
         <f>$C$4+$D$4*$H6+Q$3*$E$4</f>
         <v>72.5</v>
-      </c>
-    </row>
-    <row r="7" spans="8:17">
-      <c r="H7" s="1">
-        <v>4</v>
-      </c>
-      <c r="I7" s="1">
-        <f>$C$4+$D$4*$H7+I$3*$E$4</f>
-        <v>60</v>
-      </c>
-      <c r="J7" s="1">
-        <f>$C$4+$D$4*$H7+J$3*$E$4</f>
-        <v>63</v>
-      </c>
-      <c r="K7" s="1">
-        <f>$C$4+$D$4*$H7+K$3*$E$4</f>
-        <v>66</v>
-      </c>
-      <c r="L7" s="1">
-        <f>$C$4+$D$4*$H7+L$3*$E$4</f>
-        <v>69</v>
-      </c>
-      <c r="M7" s="1">
-        <f>$C$4+$D$4*$H7+M$3*$E$4</f>
-        <v>72</v>
-      </c>
-      <c r="N7" s="1">
-        <f>$C$4+$D$4*$H7+N$3*$E$4</f>
-        <v>75</v>
-      </c>
-      <c r="O7" s="1">
-        <f>$C$4+$D$4*$H7+O$3*$E$4</f>
-        <v>78</v>
-      </c>
-      <c r="P7" s="1">
-        <f>$C$4+$D$4*$H7+P$3*$E$4</f>
-        <v>81</v>
-      </c>
-      <c r="Q7" s="1">
-        <f>$C$4+$D$4*$H7+Q$3*$E$4</f>
-        <v>82.5</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240" activeTab="2"/>
+    <workbookView windowHeight="15160"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
@@ -2161,52 +2161,52 @@
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
       </c>
       <c r="N4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*N$3),-2)</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O4" s="1">
         <f t="shared" ref="O4:V4" si="0">ROUNDUP(EXP($H4+$D4*$I4+$J4*O$3),-2)</f>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="0"/>
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Q4" s="1">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="0"/>
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="S4" s="1">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>1700</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" si="0"/>
-        <v>4100</v>
+        <v>2600</v>
       </c>
       <c r="U4" s="1">
         <f t="shared" si="0"/>
-        <v>6700</v>
+        <v>4000</v>
       </c>
       <c r="V4" s="1">
         <f t="shared" si="0"/>
-        <v>8600</v>
+        <v>5000</v>
       </c>
       <c r="Y4" s="1">
         <v>5.5</v>
@@ -2238,52 +2238,52 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>8.9</v>
+        <v>8.2</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>0.4945</v>
+        <v>0.403</v>
       </c>
       <c r="K5" s="1">
         <v>1000</v>
       </c>
       <c r="N5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*N$3),-3)</f>
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="O5" s="1">
         <f t="shared" ref="O5:V5" si="1">ROUNDUP(EXP($H5+$D5*$I5+$J5*O$3),-3)</f>
+        <v>6000</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="1"/>
+        <v>9000</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" si="1"/>
         <v>13000</v>
       </c>
-      <c r="P5" s="1">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="Q5" s="1">
-        <f t="shared" si="1"/>
-        <v>33000</v>
-      </c>
       <c r="R5" s="1">
         <f t="shared" si="1"/>
-        <v>53000</v>
+        <v>19000</v>
       </c>
       <c r="S5" s="1">
         <f t="shared" si="1"/>
-        <v>87000</v>
+        <v>28000</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" si="1"/>
-        <v>143000</v>
+        <v>41000</v>
       </c>
       <c r="U5" s="1">
         <f t="shared" si="1"/>
-        <v>234000</v>
+        <v>62000</v>
       </c>
       <c r="V5" s="1">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>75000</v>
       </c>
       <c r="Y5" s="1">
         <v>7.7</v>
@@ -2315,52 +2315,52 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>12.4</v>
+        <v>11</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>0.4957</v>
+        <v>0.375</v>
       </c>
       <c r="K6" s="1">
         <v>10000</v>
       </c>
       <c r="N6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*N$3),-4)</f>
-        <v>250000</v>
+        <v>60000</v>
       </c>
       <c r="O6" s="1">
         <f t="shared" ref="O6:V6" si="2">ROUNDUP(EXP($H6+$D6*$I6+$J6*O$3),-4)</f>
+        <v>90000</v>
+      </c>
+      <c r="P6" s="1">
+        <f t="shared" si="2"/>
+        <v>130000</v>
+      </c>
+      <c r="Q6" s="1">
+        <f t="shared" si="2"/>
+        <v>190000</v>
+      </c>
+      <c r="R6" s="1">
+        <f t="shared" si="2"/>
+        <v>270000</v>
+      </c>
+      <c r="S6" s="1">
+        <f t="shared" si="2"/>
         <v>400000</v>
       </c>
-      <c r="P6" s="1">
-        <f t="shared" si="2"/>
-        <v>660000</v>
-      </c>
-      <c r="Q6" s="1">
-        <f t="shared" si="2"/>
-        <v>1080000</v>
-      </c>
-      <c r="R6" s="1">
-        <f t="shared" si="2"/>
-        <v>1770000</v>
-      </c>
-      <c r="S6" s="1">
-        <f t="shared" si="2"/>
-        <v>2900000</v>
-      </c>
       <c r="T6" s="1">
         <f t="shared" si="2"/>
-        <v>4760000</v>
+        <v>570000</v>
       </c>
       <c r="U6" s="1">
         <f t="shared" si="2"/>
-        <v>7810000</v>
+        <v>830000</v>
       </c>
       <c r="V6" s="1">
         <f t="shared" si="2"/>
-        <v>10000000</v>
+        <v>1000000</v>
       </c>
       <c r="Y6" s="1">
         <v>10.6</v>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,19 +4,21 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160"/>
+    <workbookView windowHeight="15160" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
     <sheet name="gold_reward_curve" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="item_luck_curve" sheetId="3" r:id="rId3"/>
+    <sheet name="item_quality_luck" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="67">
   <si>
     <t>##var</t>
   </si>
@@ -123,12 +125,6 @@
     <t>Dish</t>
   </si>
   <si>
-    <t>hidden_passive_item</t>
-  </si>
-  <si>
-    <t>PassiveItem</t>
-  </si>
-  <si>
     <t>hidden_fragment</t>
   </si>
   <si>
@@ -163,6 +159,66 @@
   </si>
   <si>
     <t>gold_default</t>
+  </si>
+  <si>
+    <t>minLuck</t>
+  </si>
+  <si>
+    <t>maxLuck</t>
+  </si>
+  <si>
+    <t>装饰品运气曲线ID。</t>
+  </si>
+  <si>
+    <t>开局基础运气。</t>
+  </si>
+  <si>
+    <t>每经过1周增加的运气。</t>
+  </si>
+  <si>
+    <t>当周每经过1天增加的运气。</t>
+  </si>
+  <si>
+    <t>指数计算的最小安全运气。</t>
+  </si>
+  <si>
+    <t>指数计算的最大安全运气。</t>
+  </si>
+  <si>
+    <t>item_luck_default</t>
+  </si>
+  <si>
+    <t>quality</t>
+  </si>
+  <si>
+    <t>baseWeight</t>
+  </si>
+  <si>
+    <t>luckGrowth</t>
+  </si>
+  <si>
+    <t>装饰品品质。</t>
+  </si>
+  <si>
+    <t>运气为0时的品质基础权重。</t>
+  </si>
+  <si>
+    <t>品质权重随运气变化的指数成长系数。</t>
+  </si>
+  <si>
+    <t>ItemQuality</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Epic</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1121,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1800" b="1" i="0" u="none">
+              <a:rPr sz="1800" b="1" i="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -1075,7 +1131,7 @@
               </a:rPr>
               <a:t>None</a:t>
             </a:r>
-            <a:endParaRPr sz="1800" b="1" i="0" u="none">
+            <a:endParaRPr sz="1800" b="1" i="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -1400,7 +1456,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1800" b="1" i="0" u="none">
+              <a:rPr sz="1800" b="1" i="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -1410,7 +1466,7 @@
               </a:rPr>
               <a:t>None</a:t>
             </a:r>
-            <a:endParaRPr sz="1800" b="1" i="0" u="none">
+            <a:endParaRPr sz="1800" b="1" i="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -1723,7 +1779,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart"/>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1753,7 +1809,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart"/>
+        <xdr:cNvPr id="3" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1987,8 +2043,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:AA8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
     <col min="2" max="2" width="26.6923076923077" style="1" customWidth="1"/>
@@ -2177,35 +2233,35 @@
         <v>200</v>
       </c>
       <c r="O4" s="1">
-        <f t="shared" ref="O4:V4" si="0">ROUNDUP(EXP($H4+$D4*$I4+$J4*O$3),-2)</f>
+        <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*O$3),-2)</f>
         <v>300</v>
       </c>
       <c r="P4" s="1">
-        <f t="shared" si="0"/>
+        <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*P$3),-2)</f>
         <v>500</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" si="0"/>
+        <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*Q$3),-2)</f>
         <v>700</v>
       </c>
       <c r="R4" s="1">
-        <f t="shared" si="0"/>
+        <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*R$3),-2)</f>
         <v>1100</v>
       </c>
       <c r="S4" s="1">
-        <f t="shared" si="0"/>
+        <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*S$3),-2)</f>
         <v>1700</v>
       </c>
       <c r="T4" s="1">
-        <f t="shared" si="0"/>
+        <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*T$3),-2)</f>
         <v>2600</v>
       </c>
       <c r="U4" s="1">
-        <f t="shared" si="0"/>
+        <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*U$3),-2)</f>
         <v>4000</v>
       </c>
       <c r="V4" s="1">
-        <f t="shared" si="0"/>
+        <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*V$3),-2)</f>
         <v>5000</v>
       </c>
       <c r="Y4" s="1">
@@ -2254,35 +2310,35 @@
         <v>4000</v>
       </c>
       <c r="O5" s="1">
-        <f t="shared" ref="O5:V5" si="1">ROUNDUP(EXP($H5+$D5*$I5+$J5*O$3),-3)</f>
+        <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*O$3),-3)</f>
         <v>6000</v>
       </c>
       <c r="P5" s="1">
-        <f t="shared" si="1"/>
+        <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*P$3),-3)</f>
         <v>9000</v>
       </c>
       <c r="Q5" s="1">
-        <f t="shared" si="1"/>
+        <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*Q$3),-3)</f>
         <v>13000</v>
       </c>
       <c r="R5" s="1">
-        <f t="shared" si="1"/>
+        <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*R$3),-3)</f>
         <v>19000</v>
       </c>
       <c r="S5" s="1">
-        <f t="shared" si="1"/>
+        <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*S$3),-3)</f>
         <v>28000</v>
       </c>
       <c r="T5" s="1">
-        <f t="shared" si="1"/>
+        <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*T$3),-3)</f>
         <v>41000</v>
       </c>
       <c r="U5" s="1">
-        <f t="shared" si="1"/>
+        <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*U$3),-3)</f>
         <v>62000</v>
       </c>
       <c r="V5" s="1">
-        <f t="shared" si="1"/>
+        <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*V$3),-3)</f>
         <v>75000</v>
       </c>
       <c r="Y5" s="1">
@@ -2331,35 +2387,35 @@
         <v>60000</v>
       </c>
       <c r="O6" s="1">
-        <f t="shared" ref="O6:V6" si="2">ROUNDUP(EXP($H6+$D6*$I6+$J6*O$3),-4)</f>
+        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*O$3),-4)</f>
         <v>90000</v>
       </c>
       <c r="P6" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*P$3),-4)</f>
         <v>130000</v>
       </c>
       <c r="Q6" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*Q$3),-4)</f>
         <v>190000</v>
       </c>
       <c r="R6" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*R$3),-4)</f>
         <v>270000</v>
       </c>
       <c r="S6" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*S$3),-4)</f>
         <v>400000</v>
       </c>
       <c r="T6" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*T$3),-4)</f>
         <v>570000</v>
       </c>
       <c r="U6" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*U$3),-4)</f>
         <v>830000</v>
       </c>
       <c r="V6" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*V$3),-4)</f>
         <v>1000000</v>
       </c>
       <c r="Y6" s="1">
@@ -2427,35 +2483,6 @@
         <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="1">
-        <v>10</v>
-      </c>
-      <c r="F9" s="1">
-        <v>10</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2471,14 +2498,14 @@
   <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.3846153846154" style="1" customWidth="1"/>
     <col min="3" max="4" width="32.1538461538462" style="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="1" customWidth="1"/>
     <col min="6" max="7" width="15.1538461538462" style="1" customWidth="1"/>
     <col min="8" max="8" width="7.84615384615385" style="1" customWidth="1"/>
     <col min="9" max="17" width="6.73076923076923" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="18" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2489,16 +2516,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2506,19 +2533,19 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -2570,7 +2597,7 @@
     </row>
     <row r="4" spans="2:17">
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1">
         <v>20</v>
@@ -2592,35 +2619,35 @@
         <v>30</v>
       </c>
       <c r="J4" s="1">
-        <f t="shared" ref="J4:Q4" si="0">$C$4+$D$4*$H4+J$3*$E$4</f>
+        <f>$C$4+$D$4*$H4+J$3*$E$4</f>
         <v>33</v>
       </c>
       <c r="K4" s="1">
-        <f t="shared" si="0"/>
+        <f>$C$4+$D$4*$H4+K$3*$E$4</f>
         <v>36</v>
       </c>
       <c r="L4" s="1">
-        <f t="shared" si="0"/>
+        <f>$C$4+$D$4*$H4+L$3*$E$4</f>
         <v>39</v>
       </c>
       <c r="M4" s="1">
-        <f t="shared" si="0"/>
+        <f>$C$4+$D$4*$H4+M$3*$E$4</f>
         <v>42</v>
       </c>
       <c r="N4" s="1">
-        <f t="shared" si="0"/>
+        <f>$C$4+$D$4*$H4+N$3*$E$4</f>
         <v>45</v>
       </c>
       <c r="O4" s="1">
-        <f t="shared" si="0"/>
+        <f>$C$4+$D$4*$H4+O$3*$E$4</f>
         <v>48</v>
       </c>
       <c r="P4" s="1">
-        <f t="shared" si="0"/>
+        <f>$C$4+$D$4*$H4+P$3*$E$4</f>
         <v>51</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" si="0"/>
+        <f>$C$4+$D$4*$H4+Q$3*$E$4</f>
         <v>52.5</v>
       </c>
     </row>
@@ -2713,6 +2740,648 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="7" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>-100</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AC13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="30.8461538461538" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="9" max="15" width="14.0769230769231"/>
+    <col min="16" max="28" width="12.9230769230769"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>6</v>
+      </c>
+      <c r="P3">
+        <v>10</v>
+      </c>
+      <c r="Q3">
+        <v>11</v>
+      </c>
+      <c r="R3">
+        <v>12</v>
+      </c>
+      <c r="S3">
+        <v>13</v>
+      </c>
+      <c r="T3">
+        <v>14</v>
+      </c>
+      <c r="U3">
+        <v>15</v>
+      </c>
+      <c r="V3">
+        <v>16</v>
+      </c>
+      <c r="W3">
+        <v>20</v>
+      </c>
+      <c r="X3">
+        <v>21</v>
+      </c>
+      <c r="Y3">
+        <v>22</v>
+      </c>
+      <c r="Z3">
+        <v>23</v>
+      </c>
+      <c r="AA3">
+        <v>24</v>
+      </c>
+      <c r="AB3">
+        <v>25</v>
+      </c>
+      <c r="AC3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:29">
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4">
+        <v>63</v>
+      </c>
+      <c r="D4">
+        <v>-0.035</v>
+      </c>
+      <c r="I4">
+        <f>$C4*EXP(I$3*$D4)</f>
+        <v>63</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:O4" si="0">$C4*EXP(J$3*$D4)</f>
+        <v>60.8331412242267</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>58.7408106540747</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>56.7204449229347</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="0"/>
+        <v>54.7695688301248</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>52.8857923084601</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>51.0668074961218</v>
+      </c>
+      <c r="P4">
+        <f t="shared" ref="P4:AC4" si="1">$C4*EXP(P$3*$D4)</f>
+        <v>44.3953496522789</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="1"/>
+        <v>42.868390080889</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="1"/>
+        <v>41.3939496483486</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="1"/>
+        <v>39.9702219807384</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="1"/>
+        <v>38.5954628336182</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="1"/>
+        <v>37.2679879551094</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="1"/>
+        <v>35.9861710224753</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="1"/>
+        <v>31.2848741388588</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="1"/>
+        <v>30.2088439154183</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="1"/>
+        <v>29.1698233036074</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="1"/>
+        <v>28.1665393732395</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="1"/>
+        <v>27.197762976032</v>
+      </c>
+      <c r="AB4">
+        <f t="shared" si="1"/>
+        <v>26.262307239746</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" si="1"/>
+        <v>25.3590261141191</v>
+      </c>
+    </row>
+    <row r="5" spans="2:29">
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>0.013</v>
+      </c>
+      <c r="I5">
+        <f>$C5*EXP(I$3*$D5)</f>
+        <v>25</v>
+      </c>
+      <c r="J5">
+        <f>$C5*EXP(J$3*$D5)</f>
+        <v>25.3271216839952</v>
+      </c>
+      <c r="K5">
+        <f>$C5*EXP(K$3*$D5)</f>
+        <v>25.6585237118361</v>
+      </c>
+      <c r="L5">
+        <f>$C5*EXP(L$3*$D5)</f>
+        <v>25.9942620912539</v>
+      </c>
+      <c r="M5">
+        <f>$C5*EXP(M$3*$D5)</f>
+        <v>26.3343935628341</v>
+      </c>
+      <c r="N5">
+        <f>$C5*EXP(N$3*$D5)</f>
+        <v>26.6789756096048</v>
+      </c>
+      <c r="O5">
+        <f>$C5*EXP(O$3*$D5)</f>
+        <v>27.0280664667521</v>
+      </c>
+      <c r="P5">
+        <f t="shared" ref="P5:AC5" si="2">$C5*EXP(P$3*$D5)</f>
+        <v>28.4707095831155</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>28.8432450416503</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="2"/>
+        <v>29.2206550772467</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>29.6030034730992</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="2"/>
+        <v>29.9903548469967</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="2"/>
+        <v>30.3827746622433</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="2"/>
+        <v>30.7803292387217</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="2"/>
+        <v>32.4232521666443</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="2"/>
+        <v>32.8475061206185</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="2"/>
+        <v>33.2773113813073</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="2"/>
+        <v>33.7127405868228</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="2"/>
+        <v>34.153867325737</v>
+      </c>
+      <c r="AB5">
+        <f t="shared" si="2"/>
+        <v>34.6007661495188</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" si="2"/>
+        <v>35.053512585133</v>
+      </c>
+    </row>
+    <row r="6" spans="2:29">
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>0.0352</v>
+      </c>
+      <c r="I6">
+        <f>$C6*EXP(I$3*$D6)</f>
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <f>$C6*EXP(J$3*$D6)</f>
+        <v>10.3582685345516</v>
+      </c>
+      <c r="K6">
+        <f>$C6*EXP(K$3*$D6)</f>
+        <v>10.7293727033881</v>
+      </c>
+      <c r="L6">
+        <f>$C6*EXP(L$3*$D6)</f>
+        <v>11.1137723668982</v>
+      </c>
+      <c r="M6">
+        <f>$C6*EXP(M$3*$D6)</f>
+        <v>11.5119438608211</v>
+      </c>
+      <c r="N6">
+        <f>$C6*EXP(N$3*$D6)</f>
+        <v>11.9243805865067</v>
+      </c>
+      <c r="O6">
+        <f>$C6*EXP(O$3*$D6)</f>
+        <v>12.351593622323</v>
+      </c>
+      <c r="P6">
+        <f t="shared" ref="P6:AC6" si="3">$C6*EXP(P$3*$D6)</f>
+        <v>14.2190852371858</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="3"/>
+        <v>14.7285103202448</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>15.256186501101</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="3"/>
+        <v>15.8027676591605</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>16.3689311002712</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="3"/>
+        <v>16.9553783960182</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="3"/>
+        <v>17.5628362530891</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="3"/>
+        <v>20.2182384982354</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="3"/>
+        <v>20.9425943660332</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="3"/>
+        <v>21.6929016253559</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="3"/>
+        <v>22.4700900329046</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="3"/>
+        <v>23.2751226556377</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="3"/>
+        <v>24.1089970641721</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="3"/>
+        <v>24.972746568941</v>
+      </c>
+    </row>
+    <row r="7" spans="2:29">
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>0.0775</v>
+      </c>
+      <c r="I7">
+        <f>$C7*EXP(I$3*$D7)</f>
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <f>$C7*EXP(J$3*$D7)</f>
+        <v>2.16116446491712</v>
+      </c>
+      <c r="K7">
+        <f>$C7*EXP(K$3*$D7)</f>
+        <v>2.33531592221025</v>
+      </c>
+      <c r="L7">
+        <f>$C7*EXP(L$3*$D7)</f>
+        <v>2.52350089271797</v>
+      </c>
+      <c r="M7">
+        <f>$C7*EXP(M$3*$D7)</f>
+        <v>2.72685022826436</v>
+      </c>
+      <c r="N7">
+        <f>$C7*EXP(N$3*$D7)</f>
+        <v>2.94658590723803</v>
+      </c>
+      <c r="O7">
+        <f>$C7*EXP(O$3*$D7)</f>
+        <v>3.1840283777742</v>
+      </c>
+      <c r="P7">
+        <f t="shared" ref="P7:AC7" si="4">$C7*EXP(P$3*$D7)</f>
+        <v>4.34118425436689</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="4"/>
+        <v>4.69100657309772</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="4"/>
+        <v>5.06901835523571</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="4"/>
+        <v>5.47749117067402</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>5.91887963747898</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>6.39583617232055</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="4"/>
+        <v>6.91122692952535</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="4"/>
+        <v>9.42294036518148</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="4"/>
+        <v>10.1822619361317</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="4"/>
+        <v>11.002771334423</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="4"/>
+        <v>11.8893992117818</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="4"/>
+        <v>12.8474735428583</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="4"/>
+        <v>13.8827516423941</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>15.0014547624059</v>
+      </c>
+    </row>
+    <row r="10" spans="9:10">
+      <c r="I10">
+        <v>63</v>
+      </c>
+      <c r="J10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="9:10">
+      <c r="I11">
+        <v>25</v>
+      </c>
+      <c r="J11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="9:10">
+      <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="9:10">
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B3:AL28"/>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="73">
   <si>
     <t>##var</t>
   </si>
@@ -197,6 +197,15 @@
     <t>luckGrowth</t>
   </si>
   <si>
+    <t>constant</t>
+  </si>
+  <si>
+    <t>minWeight</t>
+  </si>
+  <si>
+    <t>maxWeight</t>
+  </si>
+  <si>
     <t>装饰品品质。</t>
   </si>
   <si>
@@ -204,6 +213,15 @@
   </si>
   <si>
     <t>品质权重随运气变化的指数成长系数。</t>
+  </si>
+  <si>
+    <t>品质权重的常数项。</t>
+  </si>
+  <si>
+    <t>该品质权重下限。</t>
+  </si>
+  <si>
+    <t>该品质权重上限。</t>
   </si>
   <si>
     <t>ItemQuality</t>
@@ -2847,18 +2865,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="30.8461538461538" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="7" width="18" customWidth="1"/>
     <col min="9" max="15" width="14.0769230769231"/>
-    <col min="16" max="28" width="12.9230769230769"/>
+    <col min="16" max="31" width="12.9230769230769"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2871,27 +2890,45 @@
       <c r="D1" t="s">
         <v>58</v>
       </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -2899,6 +2936,15 @@
       <c r="D3" t="s">
         <v>27</v>
       </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
       <c r="I3">
         <v>0</v>
       </c>
@@ -2962,105 +3008,128 @@
       <c r="AC3">
         <v>26</v>
       </c>
+      <c r="AD3">
+        <v>36</v>
+      </c>
+      <c r="AE3">
+        <v>46</v>
+      </c>
     </row>
-    <row r="4" spans="2:29">
+    <row r="4" spans="2:31">
       <c r="B4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C4">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D4">
-        <v>-0.035</v>
+        <v>-0.0272</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
       </c>
       <c r="I4">
-        <f>$C4*EXP(I$3*$D4)</f>
-        <v>63</v>
+        <f>$C4*EXP(I$3*$D4)+$E4</f>
+        <v>65</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:O4" si="0">$C4*EXP(J$3*$D4)</f>
-        <v>60.8331412242267</v>
+        <f>$C4*EXP(J$3*$D4)+$E4</f>
+        <v>63.2558282682273</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
-        <v>58.7408106540747</v>
+        <f t="shared" ref="K4:AE4" si="0">$C4*EXP(K$3*$D4)+$E4</f>
+        <v>61.558458613838</v>
       </c>
       <c r="L4">
         <f t="shared" si="0"/>
-        <v>56.7204449229347</v>
+        <v>59.9066351774418</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>54.7695688301248</v>
+        <v>58.29913579864</v>
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
-        <v>52.8857923084601</v>
+        <v>56.7347711117668</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>51.0668074961218</v>
+        <v>55.2123836658939</v>
       </c>
       <c r="P4">
-        <f t="shared" ref="P4:AC4" si="1">$C4*EXP(P$3*$D4)</f>
-        <v>44.3953496522789</v>
+        <f t="shared" si="0"/>
+        <v>49.5205269708394</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="1"/>
-        <v>42.868390080889</v>
+        <f t="shared" si="0"/>
+        <v>48.191722304916</v>
       </c>
       <c r="R4">
-        <f t="shared" si="1"/>
-        <v>41.3939496483486</v>
+        <f t="shared" si="0"/>
+        <v>46.8985740010749</v>
       </c>
       <c r="S4">
-        <f t="shared" si="1"/>
-        <v>39.9702219807384</v>
+        <f t="shared" si="0"/>
+        <v>45.6401252774884</v>
       </c>
       <c r="T4">
-        <f t="shared" si="1"/>
-        <v>38.5954628336182</v>
+        <f t="shared" si="0"/>
+        <v>44.415445026049</v>
       </c>
       <c r="U4">
-        <f t="shared" si="1"/>
-        <v>37.2679879551094</v>
+        <f t="shared" si="0"/>
+        <v>43.2236271234561</v>
       </c>
       <c r="V4">
-        <f t="shared" si="1"/>
-        <v>35.9861710224753</v>
+        <f t="shared" si="0"/>
+        <v>42.0637897607882</v>
       </c>
       <c r="W4">
-        <f t="shared" si="1"/>
-        <v>31.2848741388588</v>
+        <f t="shared" si="0"/>
+        <v>37.7274244841483</v>
       </c>
       <c r="X4">
-        <f t="shared" si="1"/>
-        <v>30.2088439154183</v>
+        <f t="shared" si="0"/>
+        <v>36.7150689872584</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="1"/>
-        <v>29.1698233036074</v>
+        <f t="shared" si="0"/>
+        <v>35.729878441756</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="1"/>
-        <v>28.1665393732395</v>
+        <f t="shared" si="0"/>
+        <v>34.7711239193285</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="1"/>
-        <v>27.197762976032</v>
+        <f t="shared" si="0"/>
+        <v>33.8380960512969</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="1"/>
-        <v>26.262307239746</v>
+        <f t="shared" si="0"/>
+        <v>32.9301045037633</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="1"/>
-        <v>25.3590261141191</v>
+        <f t="shared" si="0"/>
+        <v>32.0464774668436</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" si="0"/>
+        <v>24.4147454110342</v>
+      </c>
+      <c r="AE4">
+        <f t="shared" si="0"/>
+        <v>18.60047782482</v>
       </c>
     </row>
-    <row r="5" spans="2:29">
+    <row r="5" spans="2:31">
       <c r="B5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>25</v>
@@ -3068,94 +3137,111 @@
       <c r="D5">
         <v>0.013</v>
       </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>40</v>
+      </c>
       <c r="I5">
-        <f>$C5*EXP(I$3*$D5)</f>
+        <f>$C5*EXP(I$3*$D5)+$E5</f>
         <v>25</v>
       </c>
       <c r="J5">
-        <f>$C5*EXP(J$3*$D5)</f>
+        <f>$C5*EXP(J$3*$D5)+$E5</f>
         <v>25.3271216839952</v>
       </c>
       <c r="K5">
-        <f>$C5*EXP(K$3*$D5)</f>
+        <f t="shared" ref="K5:AE5" si="1">$C5*EXP(K$3*$D5)+$E5</f>
         <v>25.6585237118361</v>
       </c>
       <c r="L5">
-        <f>$C5*EXP(L$3*$D5)</f>
+        <f t="shared" si="1"/>
         <v>25.9942620912539</v>
       </c>
       <c r="M5">
-        <f>$C5*EXP(M$3*$D5)</f>
+        <f t="shared" si="1"/>
         <v>26.3343935628341</v>
       </c>
       <c r="N5">
-        <f>$C5*EXP(N$3*$D5)</f>
+        <f t="shared" si="1"/>
         <v>26.6789756096048</v>
       </c>
       <c r="O5">
-        <f>$C5*EXP(O$3*$D5)</f>
+        <f t="shared" si="1"/>
         <v>27.0280664667521</v>
       </c>
       <c r="P5">
-        <f t="shared" ref="P5:AC5" si="2">$C5*EXP(P$3*$D5)</f>
+        <f t="shared" si="1"/>
         <v>28.4707095831155</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>28.8432450416503</v>
       </c>
       <c r="R5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>29.2206550772467</v>
       </c>
       <c r="S5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>29.6030034730992</v>
       </c>
       <c r="T5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>29.9903548469967</v>
       </c>
       <c r="U5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>30.3827746622433</v>
       </c>
       <c r="V5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>30.7803292387217</v>
       </c>
       <c r="W5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>32.4232521666443</v>
       </c>
       <c r="X5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>32.8475061206185</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>33.2773113813073</v>
       </c>
       <c r="Z5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>33.7127405868228</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>34.153867325737</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>34.6007661495188</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>35.053512585133</v>
       </c>
+      <c r="AD5">
+        <f t="shared" si="1"/>
+        <v>39.9199350671763</v>
+      </c>
+      <c r="AE5">
+        <f t="shared" si="1"/>
+        <v>45.4619551149763</v>
+      </c>
     </row>
-    <row r="6" spans="2:29">
+    <row r="6" spans="2:31">
       <c r="B6" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -3163,192 +3249,226 @@
       <c r="D6">
         <v>0.0352</v>
       </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>35</v>
+      </c>
       <c r="I6">
-        <f>$C6*EXP(I$3*$D6)</f>
+        <f>$C6*EXP(I$3*$D6)+$E6</f>
         <v>10</v>
       </c>
       <c r="J6">
-        <f>$C6*EXP(J$3*$D6)</f>
+        <f>$C6*EXP(J$3*$D6)+$E6</f>
         <v>10.3582685345516</v>
       </c>
       <c r="K6">
-        <f>$C6*EXP(K$3*$D6)</f>
+        <f t="shared" ref="K6:AE6" si="2">$C6*EXP(K$3*$D6)+$E6</f>
         <v>10.7293727033881</v>
       </c>
       <c r="L6">
-        <f>$C6*EXP(L$3*$D6)</f>
+        <f t="shared" si="2"/>
         <v>11.1137723668982</v>
       </c>
       <c r="M6">
-        <f>$C6*EXP(M$3*$D6)</f>
+        <f t="shared" si="2"/>
         <v>11.5119438608211</v>
       </c>
       <c r="N6">
-        <f>$C6*EXP(N$3*$D6)</f>
+        <f t="shared" si="2"/>
         <v>11.9243805865067</v>
       </c>
       <c r="O6">
-        <f>$C6*EXP(O$3*$D6)</f>
+        <f t="shared" si="2"/>
         <v>12.351593622323</v>
       </c>
       <c r="P6">
-        <f t="shared" ref="P6:AC6" si="3">$C6*EXP(P$3*$D6)</f>
+        <f t="shared" si="2"/>
         <v>14.2190852371858</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>14.7285103202448</v>
       </c>
       <c r="R6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>15.256186501101</v>
       </c>
       <c r="S6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>15.8027676591605</v>
       </c>
       <c r="T6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>16.3689311002712</v>
       </c>
       <c r="U6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>16.9553783960182</v>
       </c>
       <c r="V6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>17.5628362530891</v>
       </c>
       <c r="W6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20.2182384982354</v>
       </c>
       <c r="X6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20.9425943660332</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>21.6929016253559</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>22.4700900329046</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>23.2751226556377</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>24.1089970641721</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>24.972746568941</v>
       </c>
+      <c r="AD6">
+        <f t="shared" si="2"/>
+        <v>35.5089612070411</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="2"/>
+        <v>50.4904946086841</v>
+      </c>
     </row>
-    <row r="7" spans="2:29">
+    <row r="7" spans="2:31">
       <c r="B7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>0.0775</v>
+        <v>0.031</v>
+      </c>
+      <c r="E7">
+        <v>-10</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>15</v>
       </c>
       <c r="I7">
-        <f>$C7*EXP(I$3*$D7)</f>
-        <v>2</v>
+        <f>$C7*EXP(I$3*$D7)+$E7</f>
+        <v>-2</v>
       </c>
       <c r="J7">
-        <f>$C7*EXP(J$3*$D7)</f>
-        <v>2.16116446491712</v>
+        <f>$C7*EXP(J$3*$D7)+$E7</f>
+        <v>-1.74811596890782</v>
       </c>
       <c r="K7">
-        <f>$C7*EXP(K$3*$D7)</f>
-        <v>2.33531592221025</v>
+        <f t="shared" ref="K7:AE7" si="3">$C7*EXP(K$3*$D7)+$E7</f>
+        <v>-1.48830124217573</v>
       </c>
       <c r="L7">
-        <f>$C7*EXP(L$3*$D7)</f>
-        <v>2.52350089271797</v>
+        <f t="shared" si="3"/>
+        <v>-1.22030611785534</v>
       </c>
       <c r="M7">
-        <f>$C7*EXP(M$3*$D7)</f>
-        <v>2.72685022826436</v>
+        <f t="shared" si="3"/>
+        <v>-0.943873032006598</v>
       </c>
       <c r="N7">
-        <f>$C7*EXP(N$3*$D7)</f>
-        <v>2.94658590723803</v>
+        <f t="shared" si="3"/>
+        <v>-0.658736311159</v>
       </c>
       <c r="O7">
-        <f>$C7*EXP(O$3*$D7)</f>
-        <v>3.1840283777742</v>
+        <f t="shared" si="3"/>
+        <v>-0.364621916978962</v>
       </c>
       <c r="P7">
-        <f t="shared" ref="P7:AC7" si="4">$C7*EXP(P$3*$D7)</f>
-        <v>4.34118425436689</v>
+        <f t="shared" si="3"/>
+        <v>0.907400913057423</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="4"/>
-        <v>4.69100657309772</v>
+        <f t="shared" si="3"/>
+        <v>1.25082592689735</v>
       </c>
       <c r="R7">
-        <f t="shared" si="4"/>
-        <v>5.06901835523571</v>
+        <f t="shared" si="3"/>
+        <v>1.60506385034527</v>
       </c>
       <c r="S7">
-        <f t="shared" si="4"/>
-        <v>5.47749117067402</v>
+        <f t="shared" si="3"/>
+        <v>1.97045513330866</v>
       </c>
       <c r="T7">
-        <f t="shared" si="4"/>
-        <v>5.91887963747898</v>
+        <f t="shared" si="3"/>
+        <v>2.3473509449319</v>
       </c>
       <c r="U7">
-        <f t="shared" si="4"/>
-        <v>6.39583617232055</v>
+        <f t="shared" si="3"/>
+        <v>2.73611351109681</v>
       </c>
       <c r="V7">
-        <f t="shared" si="4"/>
-        <v>6.91122692952535</v>
+        <f t="shared" si="3"/>
+        <v>3.13711646254964</v>
       </c>
       <c r="W7">
-        <f t="shared" si="4"/>
-        <v>9.42294036518148</v>
+        <f t="shared" si="3"/>
+        <v>4.87142433477074</v>
       </c>
       <c r="X7">
-        <f t="shared" si="4"/>
-        <v>10.1822619361317</v>
+        <f t="shared" si="3"/>
+        <v>5.33965862346129</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="4"/>
-        <v>11.002771334423</v>
+        <f t="shared" si="3"/>
+        <v>5.82263550466821</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="4"/>
-        <v>11.8893992117818</v>
+        <f t="shared" si="3"/>
+        <v>6.32081915634548</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="4"/>
-        <v>12.8474735428583</v>
+        <f t="shared" si="3"/>
+        <v>6.83468837132382</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="4"/>
-        <v>13.8827516423941</v>
+        <f t="shared" si="3"/>
+        <v>7.36473701746754</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="4"/>
-        <v>15.0014547624059</v>
+        <f t="shared" si="3"/>
+        <v>7.91147451231946</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="3"/>
+        <v>14.4209541812348</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" si="3"/>
+        <v>23.2961422417667</v>
       </c>
     </row>
     <row r="10" spans="9:10">
       <c r="I10">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J10">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="9:10">
@@ -3369,10 +3489,10 @@
     </row>
     <row r="13" spans="9:10">
       <c r="I13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160" activeTab="3"/>
+    <workbookView windowHeight="15160"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
@@ -2454,7 +2454,7 @@
         <v>34</v>
       </c>
       <c r="E7" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
         <v>10</v>
@@ -2483,7 +2483,7 @@
         <v>36</v>
       </c>
       <c r="E8" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
         <v>10</v>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160"/>
+    <workbookView windowHeight="15160" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -2264,23 +2264,23 @@
       </c>
       <c r="R4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*R$3),-2)</f>
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="S4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*S$3),-2)</f>
-        <v>1700</v>
+        <v>1400</v>
       </c>
       <c r="T4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*T$3),-2)</f>
-        <v>2600</v>
+        <v>2000</v>
       </c>
       <c r="U4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*U$3),-2)</f>
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="V4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*V$3),-2)</f>
-        <v>5000</v>
+        <v>3700</v>
       </c>
       <c r="Y4" s="1">
         <v>5.5</v>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160" activeTab="3"/>
+    <workbookView windowHeight="15160"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
@@ -2454,7 +2454,7 @@
         <v>34</v>
       </c>
       <c r="E7" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7" s="1">
         <v>10</v>
@@ -2483,7 +2483,7 @@
         <v>36</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1">
         <v>10</v>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160"/>
+    <workbookView windowHeight="15160" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -2256,31 +2256,31 @@
       </c>
       <c r="P4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*P$3),-2)</f>
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*Q$3),-2)</f>
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="R4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*R$3),-2)</f>
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="S4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*S$3),-2)</f>
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="T4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*T$3),-2)</f>
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="U4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*U$3),-2)</f>
-        <v>3000</v>
+        <v>2300</v>
       </c>
       <c r="V4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*V$3),-2)</f>
-        <v>3700</v>
+        <v>2700</v>
       </c>
       <c r="Y4" s="1">
         <v>5.5</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>0.403</v>
+        <v>0.534</v>
       </c>
       <c r="K5" s="1">
         <v>1000</v>
@@ -2329,35 +2329,35 @@
       </c>
       <c r="O5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*O$3),-3)</f>
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="P5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*P$3),-3)</f>
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="Q5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*Q$3),-3)</f>
-        <v>13000</v>
+        <v>19000</v>
       </c>
       <c r="R5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*R$3),-3)</f>
-        <v>19000</v>
+        <v>31000</v>
       </c>
       <c r="S5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*S$3),-3)</f>
-        <v>28000</v>
+        <v>53000</v>
       </c>
       <c r="T5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*T$3),-3)</f>
-        <v>41000</v>
+        <v>90000</v>
       </c>
       <c r="U5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*U$3),-3)</f>
-        <v>62000</v>
+        <v>153000</v>
       </c>
       <c r="V5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*V$3),-3)</f>
-        <v>75000</v>
+        <v>200000</v>
       </c>
       <c r="Y5" s="1">
         <v>7.7</v>
@@ -2389,52 +2389,52 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>0.375</v>
+        <v>0.6157</v>
       </c>
       <c r="K6" s="1">
         <v>10000</v>
       </c>
       <c r="N6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*N$3),-4)</f>
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="O6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*O$3),-4)</f>
-        <v>90000</v>
+        <v>190000</v>
       </c>
       <c r="P6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*P$3),-4)</f>
-        <v>130000</v>
+        <v>340000</v>
       </c>
       <c r="Q6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*Q$3),-4)</f>
-        <v>190000</v>
+        <v>630000</v>
       </c>
       <c r="R6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*R$3),-4)</f>
-        <v>270000</v>
+        <v>1160000</v>
       </c>
       <c r="S6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*S$3),-4)</f>
-        <v>400000</v>
+        <v>2150000</v>
       </c>
       <c r="T6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*T$3),-4)</f>
-        <v>570000</v>
+        <v>3970000</v>
       </c>
       <c r="U6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*U$3),-4)</f>
-        <v>830000</v>
+        <v>7350000</v>
       </c>
       <c r="V6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*V$3),-4)</f>
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="Y6" s="1">
         <v>10.6</v>
@@ -3356,19 +3356,19 @@
         <v>72</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>0.031</v>
       </c>
       <c r="E7">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <f>$C7*EXP(I$3*$D7)+$E7</f>
@@ -3376,91 +3376,91 @@
       </c>
       <c r="J7">
         <f>$C7*EXP(J$3*$D7)+$E7</f>
-        <v>-1.74811596890782</v>
+        <v>-1.84257248056739</v>
       </c>
       <c r="K7">
         <f t="shared" ref="K7:AE7" si="3">$C7*EXP(K$3*$D7)+$E7</f>
-        <v>-1.48830124217573</v>
+        <v>-1.68018827635983</v>
       </c>
       <c r="L7">
         <f t="shared" si="3"/>
-        <v>-1.22030611785534</v>
+        <v>-1.51269132365959</v>
       </c>
       <c r="M7">
         <f t="shared" si="3"/>
-        <v>-0.943873032006598</v>
+        <v>-1.33992064500412</v>
       </c>
       <c r="N7">
         <f t="shared" si="3"/>
-        <v>-0.658736311159</v>
+        <v>-1.16171019447438</v>
       </c>
       <c r="O7">
         <f t="shared" si="3"/>
-        <v>-0.364621916978962</v>
+        <v>-0.977888698111851</v>
       </c>
       <c r="P7">
         <f t="shared" si="3"/>
-        <v>0.907400913057423</v>
+        <v>-0.182874429339111</v>
       </c>
       <c r="Q7">
         <f t="shared" si="3"/>
-        <v>1.25082592689735</v>
+        <v>0.0317662043108449</v>
       </c>
       <c r="R7">
         <f t="shared" si="3"/>
-        <v>1.60506385034527</v>
+        <v>0.253164906465795</v>
       </c>
       <c r="S7">
         <f t="shared" si="3"/>
-        <v>1.97045513330866</v>
+        <v>0.481534458317913</v>
       </c>
       <c r="T7">
         <f t="shared" si="3"/>
-        <v>2.3473509449319</v>
+        <v>0.717094340582435</v>
       </c>
       <c r="U7">
         <f t="shared" si="3"/>
-        <v>2.73611351109681</v>
+        <v>0.960070944435506</v>
       </c>
       <c r="V7">
         <f t="shared" si="3"/>
-        <v>3.13711646254964</v>
+        <v>1.21069778909353</v>
       </c>
       <c r="W7">
         <f t="shared" si="3"/>
-        <v>4.87142433477074</v>
+        <v>2.29464020923171</v>
       </c>
       <c r="X7">
         <f t="shared" si="3"/>
-        <v>5.33965862346129</v>
+        <v>2.58728663966331</v>
       </c>
       <c r="Y7">
         <f t="shared" si="3"/>
-        <v>5.82263550466821</v>
+        <v>2.88914719041763</v>
       </c>
       <c r="Z7">
         <f t="shared" si="3"/>
-        <v>6.32081915634548</v>
+        <v>3.20051197271592</v>
       </c>
       <c r="AA7">
         <f t="shared" si="3"/>
-        <v>6.83468837132382</v>
+        <v>3.52168023207739</v>
       </c>
       <c r="AB7">
         <f t="shared" si="3"/>
-        <v>7.36473701746754</v>
+        <v>3.85296063591721</v>
       </c>
       <c r="AC7">
         <f t="shared" si="3"/>
-        <v>7.91147451231946</v>
+        <v>4.19467157019966</v>
       </c>
       <c r="AD7">
         <f t="shared" si="3"/>
-        <v>14.4209541812348</v>
+        <v>8.26309636327172</v>
       </c>
       <c r="AE7">
         <f t="shared" si="3"/>
-        <v>23.2961422417667</v>
+        <v>13.8100889011042</v>
       </c>
     </row>
     <row r="10" spans="9:10">
@@ -3492,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160" activeTab="3"/>
+    <workbookView windowHeight="15160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
@@ -2513,8 +2513,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.3846153846154" style="1" customWidth="1"/>
@@ -2618,55 +2618,55 @@
         <v>46</v>
       </c>
       <c r="C4" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E4" s="1">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F4" s="1">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="I4" s="1">
         <f>$C$4+$D$4*$H4+I$3*$E$4</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J4" s="1">
         <f>$C$4+$D$4*$H4+J$3*$E$4</f>
-        <v>33</v>
+        <v>29.5</v>
       </c>
       <c r="K4" s="1">
         <f>$C$4+$D$4*$H4+K$3*$E$4</f>
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L4" s="1">
         <f>$C$4+$D$4*$H4+L$3*$E$4</f>
-        <v>39</v>
+        <v>32.5</v>
       </c>
       <c r="M4" s="1">
         <f>$C$4+$D$4*$H4+M$3*$E$4</f>
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="N4" s="1">
         <f>$C$4+$D$4*$H4+N$3*$E$4</f>
-        <v>45</v>
+        <v>35.5</v>
       </c>
       <c r="O4" s="1">
         <f>$C$4+$D$4*$H4+O$3*$E$4</f>
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="P4" s="1">
         <f>$C$4+$D$4*$H4+P$3*$E$4</f>
-        <v>51</v>
+        <v>38.5</v>
       </c>
       <c r="Q4" s="1">
         <f>$C$4+$D$4*$H4+Q$3*$E$4</f>
-        <v>52.5</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="5" spans="8:17">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="I5" s="1">
         <f>$C$4+$D$4*$H5+I$3*$E$4</f>
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J5" s="1">
         <f>$C$4+$D$4*$H5+J$3*$E$4</f>
-        <v>43</v>
+        <v>33.5</v>
       </c>
       <c r="K5" s="1">
         <f>$C$4+$D$4*$H5+K$3*$E$4</f>
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="L5" s="1">
         <f>$C$4+$D$4*$H5+L$3*$E$4</f>
-        <v>49</v>
+        <v>36.5</v>
       </c>
       <c r="M5" s="1">
         <f>$C$4+$D$4*$H5+M$3*$E$4</f>
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="N5" s="1">
         <f>$C$4+$D$4*$H5+N$3*$E$4</f>
-        <v>55</v>
+        <v>39.5</v>
       </c>
       <c r="O5" s="1">
         <f>$C$4+$D$4*$H5+O$3*$E$4</f>
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="P5" s="1">
         <f>$C$4+$D$4*$H5+P$3*$E$4</f>
-        <v>61</v>
+        <v>42.5</v>
       </c>
       <c r="Q5" s="1">
         <f>$C$4+$D$4*$H5+Q$3*$E$4</f>
-        <v>62.5</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="6" spans="8:17">
@@ -2716,39 +2716,54 @@
       </c>
       <c r="I6" s="1">
         <f>$C$4+$D$4*$H6+I$3*$E$4</f>
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J6" s="1">
         <f>$C$4+$D$4*$H6+J$3*$E$4</f>
-        <v>53</v>
+        <v>37.5</v>
       </c>
       <c r="K6" s="1">
         <f>$C$4+$D$4*$H6+K$3*$E$4</f>
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="L6" s="1">
         <f>$C$4+$D$4*$H6+L$3*$E$4</f>
-        <v>59</v>
+        <v>40.5</v>
       </c>
       <c r="M6" s="1">
         <f>$C$4+$D$4*$H6+M$3*$E$4</f>
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="N6" s="1">
         <f>$C$4+$D$4*$H6+N$3*$E$4</f>
-        <v>65</v>
+        <v>43.5</v>
       </c>
       <c r="O6" s="1">
         <f>$C$4+$D$4*$H6+O$3*$E$4</f>
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P6" s="1">
         <f>$C$4+$D$4*$H6+P$3*$E$4</f>
-        <v>71</v>
+        <v>46.5</v>
       </c>
       <c r="Q6" s="1">
         <f>$C$4+$D$4*$H6+Q$3*$E$4</f>
-        <v>72.5</v>
+        <v>47.25</v>
+      </c>
+    </row>
+    <row r="8" spans="12:12">
+      <c r="L8" s="1">
+        <f>SUM(I4:P6)</f>
+        <v>894</v>
+      </c>
+    </row>
+    <row r="9" spans="12:14">
+      <c r="L9" s="1">
+        <v>1212</v>
+      </c>
+      <c r="N9" s="1">
+        <f>L8/L9</f>
+        <v>0.737623762376238</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/curve.xlsx
+++ b/GourmetProject/GameConfig/Datas/curve.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160" activeTab="1"/>
+    <workbookView windowHeight="15160"/>
   </bookViews>
   <sheets>
     <sheet name="hidden_score_curve" sheetId="1" r:id="rId1"/>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -2268,19 +2268,19 @@
       </c>
       <c r="S4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*S$3),-2)</f>
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="T4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*T$3),-2)</f>
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="U4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*U$3),-2)</f>
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="V4" s="1">
         <f>ROUNDUP(EXP($H4+$D4*$I4+$J4*V$3),-2)</f>
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="Y4" s="1">
         <v>5.5</v>
@@ -2312,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>8.2</v>
+        <v>7.5</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
@@ -2325,39 +2325,39 @@
       </c>
       <c r="N5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*N$3),-3)</f>
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="O5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*O$3),-3)</f>
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="P5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*P$3),-3)</f>
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="Q5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*Q$3),-3)</f>
-        <v>19000</v>
+        <v>9000</v>
       </c>
       <c r="R5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*R$3),-3)</f>
-        <v>31000</v>
+        <v>16000</v>
       </c>
       <c r="S5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*S$3),-3)</f>
-        <v>53000</v>
+        <v>27000</v>
       </c>
       <c r="T5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*T$3),-3)</f>
-        <v>90000</v>
+        <v>45000</v>
       </c>
       <c r="U5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*U$3),-3)</f>
-        <v>153000</v>
+        <v>76000</v>
       </c>
       <c r="V5" s="1">
         <f>ROUNDUP(EXP($H5+$D5*$I5+$J5*V$3),-3)</f>
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="Y5" s="1">
         <v>7.7</v>
@@ -2389,52 +2389,52 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>0.6157</v>
+        <v>0.5631</v>
       </c>
       <c r="K6" s="1">
         <v>10000</v>
       </c>
       <c r="N6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*N$3),-4)</f>
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="O6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*O$3),-4)</f>
-        <v>190000</v>
+        <v>130000</v>
       </c>
       <c r="P6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*P$3),-4)</f>
-        <v>340000</v>
+        <v>230000</v>
       </c>
       <c r="Q6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*Q$3),-4)</f>
-        <v>630000</v>
+        <v>400000</v>
       </c>
       <c r="R6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*R$3),-4)</f>
-        <v>1160000</v>
+        <v>700000</v>
       </c>
       <c r="S6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*S$3),-4)</f>
-        <v>2150000</v>
+        <v>1230000</v>
       </c>
       <c r="T6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*T$3),-4)</f>
-        <v>3970000</v>
+        <v>2150000</v>
       </c>
       <c r="U6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*U$3),-4)</f>
-        <v>7350000</v>
+        <v>3770000</v>
       </c>
       <c r="V6" s="1">
         <f>ROUNDUP(EXP($H6+$D6*$I6+$J6*V$3),-4)</f>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="Y6" s="1">
         <v>10.6</v>
